--- a/public/template/template_bulk_ita.xlsx
+++ b/public/template/template_bulk_ita.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Kerjaan\Bjb\Aplikasi AMT\Back Office\App\Devel\backoff\public\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\mtm\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB44B19-BB8C-410E-B11C-EB8E24C6A152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B5A182-C906-4B47-B27D-58793060B4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -404,19 +404,18 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="26.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.77734375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.21875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.77734375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.21875" style="2"/>
+    <col min="4" max="4" width="17.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.21875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -507,11 +506,11 @@
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Rekening Eksternal Debit" error="Inputan tidak boleh kurang atau lebih dari 13 karakter." promptTitle="Input Validation" prompt="Inputan tidak boleh kurang atau lebih dari 13 karakter." sqref="F2:F1048576" xr:uid="{3CE9FF78-8130-4AFE-ADA3-5AA597A7C8D8}">
       <formula1>13</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 1" error="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." sqref="K2:K1048576" xr:uid="{0AEB2DE0-0F40-42E9-94F1-21DBB6B47858}">
-      <formula1>AND(ISERROR(FIND("?",K2)), ISERROR(FIND(":",K2)), ISERROR(FIND("*",K2)))</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 2" error="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." sqref="L2:L1048576" xr:uid="{F6E333E0-B4BC-4526-9A44-E4D8E077F297}">
-      <formula1>AND(ISERROR(FIND("?",L2)), ISERROR(FIND(":",L2)), ISERROR(FIND("*",L2)))</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 1" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="K2:K1048576" xr:uid="{0AEB2DE0-0F40-42E9-94F1-21DBB6B47858}">
+      <formula1>AND(ISERROR(FIND("?",K2)), ISERROR(FIND(":",K2)), ISERROR(FIND("*",K2)), LEN(K2)&lt;=35)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 2" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="L2:L1048576" xr:uid="{F6E333E0-B4BC-4526-9A44-E4D8E077F297}">
+      <formula1>AND(ISERROR(FIND("?",L2)), ISERROR(FIND(":",L2)), ISERROR(FIND("*",L2)), LEN(L2)&lt;=35)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/template/template_bulk_ita.xlsx
+++ b/public/template/template_bulk_ita.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\mtm\public\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\apuppt\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B5A182-C906-4B47-B27D-58793060B4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850C86CF-58CF-402B-82C4-D5E0B152DA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -404,17 +407,17 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.21875" style="2"/>
   </cols>
   <sheetData>
